--- a/라리가_2026-2027.xlsx
+++ b/라리가_2026-2027.xlsx
@@ -545,12 +545,12 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>08.17</t>
+          <t>08.16</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>02:30</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -639,79 +639,79 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>08.17</t>
+          <t>08.16</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>04:30</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>AT 마드리드</t>
+          <t>세비야</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr"/>
       <c r="I3" s="2" t="inlineStr"/>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>말라가</t>
+          <t>라요 바예카노</t>
         </is>
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>5.50</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>8.00</t>
+          <t>3.20</t>
         </is>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2/2.5</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="R3" s="2" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>1.98</t>
         </is>
       </c>
       <c r="S3" s="2" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>0/0.5</t>
         </is>
       </c>
       <c r="T3" s="2" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>1.88</t>
         </is>
       </c>
     </row>
@@ -743,69 +743,69 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>바르셀로나</t>
+          <t>라싱 산탄데르</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr"/>
       <c r="I4" s="2" t="inlineStr"/>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>15</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>아틀레틱 빌바오</t>
+          <t>비야레알</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>3.30</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>3.40</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>7.00</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
           <t>2.00</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>3/3.5</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>0/-0.5</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
         <is>
           <t>1.85</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>1.83</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>1/1.5</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>2.03</t>
         </is>
       </c>
     </row>
@@ -832,39 +832,39 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>02:00</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>셀타비고</t>
+          <t>에스파뇰</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr"/>
       <c r="I5" s="2" t="inlineStr"/>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>12</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>오사수나</t>
+          <t>레반테</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>3.40</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -874,17 +874,17 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>2/2.5</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="R5" s="2" t="inlineStr">
@@ -926,49 +926,49 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>04:30</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>데포르티보</t>
+          <t>셀타비고</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>17</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr"/>
       <c r="I6" s="2" t="inlineStr"/>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>7</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>엘체</t>
+          <t>오사수나</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>3.60</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -978,22 +978,22 @@
       </c>
       <c r="Q6" s="2" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1.98</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>0/0.5</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1.88</t>
+          <t>1.80</t>
         </is>
       </c>
     </row>
@@ -1015,79 +1015,79 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>08.17</t>
+          <t>08.18</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>04:00</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>에스파뇰</t>
+          <t>데포르티보</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr"/>
       <c r="I7" s="2" t="inlineStr"/>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>18</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>레반테</t>
+          <t>엘체</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>3.20</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>2/2.5</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>1.98</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0/0.5</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>1.88</t>
         </is>
       </c>
     </row>
@@ -1109,79 +1109,79 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>08.17</t>
+          <t>08.20</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>04:00</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>라싱 산탄데르</t>
+          <t>AT 마드리드</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>16</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr"/>
       <c r="I8" s="2" t="inlineStr"/>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>11</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>비야레알</t>
+          <t>말라가</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>5.50</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>8.00</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
           <t>1.95</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>2.5</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>1.90</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>2.00</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>0/-0.5</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>1.85</t>
         </is>
       </c>
     </row>
@@ -1203,79 +1203,79 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>08.17</t>
+          <t>08.26</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>04:00</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>레알 마드리드</t>
+          <t>발렌시아</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr"/>
       <c r="I9" s="2" t="inlineStr"/>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>8</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>레알소시에다드</t>
+          <t>베티스</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>2.60</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>4.50</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>8.00</t>
+          <t>2.63</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1/1.5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>1.95</t>
         </is>
       </c>
     </row>
@@ -1297,79 +1297,79 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>08.17</t>
+          <t>08.27</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>04:00</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>세비야</t>
+          <t>레알 마드리드</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr"/>
       <c r="I10" s="2" t="inlineStr"/>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>14</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>라요 바예카노</t>
+          <t>레알소시에다드</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>4.50</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>8.00</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
+          <t>1.83</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
           <t>2.03</t>
         </is>
       </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>2/2.5</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
+      <c r="R10" s="2" t="inlineStr">
         <is>
           <t>1.83</t>
         </is>
       </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>1.98</t>
-        </is>
-      </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>0/0.5</t>
+          <t>1/1.5</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1.88</t>
+          <t>2.03</t>
         </is>
       </c>
     </row>
@@ -1391,49 +1391,49 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>08.17</t>
+          <t>08.28</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>04:00</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>발렌시아</t>
+          <t>바르셀로나</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr"/>
       <c r="I11" s="2" t="inlineStr"/>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>베티스</t>
+          <t>아틀레틱 빌바오</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2.60</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>4.75</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>2.63</t>
+          <t>7.00</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
@@ -1443,7 +1443,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>3/3.5</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1453,17 +1453,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1/1.5</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>2.03</t>
         </is>
       </c>
     </row>
